--- a/presentations/heatmap_byhand/xlsx/baseline_methods/owasp_risk_rating/mcp_sqlite_risk_rankings_owasp.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/owasp_risk_rating/mcp_sqlite_risk_rankings_owasp.xlsx
@@ -1767,12 +1767,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1791,6 +1792,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1806,6 +1812,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L=(7+6+8+9)/4=7.5(High); I=(9-3+9-2)/2=(6,7) High; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1821,6 +1832,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L=(7+7+8+9)/4=7.75(High); I=(9-2+9-1)/2=(7,8) High; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1836,6 +1852,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L=(7+8+8+9)/4=8.0(High); I=(9+9)/2=9.0 High; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1851,6 +1872,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L=(7+9+7+9)/4=8.0(High); I=(9+1+9+1)/2=9.0 High; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1866,6 +1892,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>L=(7+7+7+9)/4=7.5(High); I=(9-1+9)/2=(8,9) High; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
@@ -1879,6 +1910,11 @@
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L=(7+6+7+9)/4=7.25(High); I=(9-1+9)/2=(8,9) High; matrix(H,H) → Critical</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1930,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1918,6 +1955,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1933,6 +1975,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SQLITE_IMPACT (9,9) for employees/PII; read_query I=9.0 High; L=8.0 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1948,6 +1995,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SQLITE_IMPACT max (9,9) grants/Financial; write_query I cap=9; L=8.0 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1963,6 +2015,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SQLITE_IMPACT (9,9) api_keys; write_query I=(9+1)cap=9; L=8.0 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1978,6 +2035,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>experiments (8,8); write_query I=(8+1,8+1)=9 High; L=8.0 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -1993,6 +2055,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>publications (3,3); write_query I=(3+1,3+1)=(4,4) Med; L=8.0 High → High</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2008,6 +2075,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>employees Role/Org (7,6); write I=(7+1,6+1)=High; L=7.75 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2021,6 +2093,11 @@
       <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>projects Timeline (5,5); write_query I=(5+1,5+1)=(6,6) High; L=7.25 High → Critical</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2112,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2059,6 +2137,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -2074,6 +2157,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>employees PII (9,9); write I=cap 9; L=8.0 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -2089,6 +2177,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>projects max (7,7) ResMetadata; write I=(8,8) High; L=7.75 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2104,6 +2197,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>datasets max (7,6) InternalData; write I=(8,7) High; L=7.75 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -2119,6 +2217,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>experiments ResResults (8,8); write I=(9,9); L=7.75 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2134,6 +2237,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>publications PublicOutput (3,3); write I=(4,4) Med; L=7.25 High → High</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -2149,6 +2257,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>grants Financial (8,8); write I=(9,9) High; L=8.0 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2162,6 +2275,11 @@
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>api_keys Credentials (9,9); write I=cap 9; L=8.0 High; matrix(H,H) → Critical</t>
         </is>
       </c>
     </row>
